--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782BC8F8-F3CE-40CE-B3EA-BFA125998358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782BC8F8-F3CE-40CE-B3EA-BFA125998358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B690E1E0-04DE-46FE-B93F-B93DC45892F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>0.1</t>
+  </si>
+  <si>
+    <t>h_max</t>
   </si>
 </sst>
 </file>
@@ -5381,13 +5384,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,8 +5415,11 @@
       <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5438,8 +5444,11 @@
       <c r="H2" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5463,6 +5472,9 @@
       </c>
       <c r="H3" s="3">
         <v>1000</v>
+      </c>
+      <c r="I3" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED1D54-31C4-4098-B063-43E9E8FA74D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50151E09-B5F2-472C-BEDF-F8141D06AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>h_max</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1019,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1233,6 +1236,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1541,36 +1547,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1760,7 +1766,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -1855,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -1950,7 +1956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -2045,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -2141,9 +2147,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2153,13 +2159,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -2191,7 +2197,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2223,7 +2229,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>165</v>
       </c>
@@ -2264,9 +2270,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2292,7 +2298,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2318,7 +2324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2355,17 +2361,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2391,7 +2397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2417,7 +2423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>0</v>
       </c>
@@ -2443,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -2469,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -2495,7 +2501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
@@ -2521,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -2547,7 +2553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -2573,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>6</v>
       </c>
@@ -2599,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -2625,7 +2631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -2651,7 +2657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>9</v>
       </c>
@@ -2677,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -2703,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -2729,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -2755,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>13</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -2807,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -2833,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>16</v>
       </c>
@@ -2859,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -2885,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -2911,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>19</v>
       </c>
@@ -2937,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -2963,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -2989,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -3015,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>23</v>
       </c>
@@ -3041,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -3067,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>25</v>
       </c>
@@ -3093,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -3119,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -3145,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>28</v>
       </c>
@@ -3171,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -3197,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -3223,7 +3229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>31</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -3275,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -3301,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52">
         <v>34</v>
       </c>
@@ -3327,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -3353,7 +3359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -3379,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -3405,7 +3411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>38</v>
       </c>
@@ -3431,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -3457,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -3483,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -3509,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -3535,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -3561,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -3587,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -3613,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -3639,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -3665,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -3691,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -3717,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -3743,7 +3749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -3769,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -3795,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -3821,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -3873,7 +3879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -3899,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -3925,7 +3931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -3951,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -3977,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -4003,7 +4009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -4029,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -4055,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -4081,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -4107,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -4133,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -4159,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -4185,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -4211,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -4237,7 +4243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -4263,7 +4269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -4289,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -4315,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -4341,7 +4347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -4367,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -4393,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -4419,7 +4425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -4445,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -4471,7 +4477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -4497,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -4523,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -4549,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -4575,7 +4581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -4601,7 +4607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -4627,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -4653,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -4679,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -4705,7 +4711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -4757,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -4783,7 +4789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -4809,7 +4815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -4835,7 +4841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -4861,10 +4867,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4872,7 +4878,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4880,7 +4886,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4888,7 +4894,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4896,7 +4902,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4904,7 +4910,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4912,7 +4918,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4920,7 +4926,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4928,7 +4934,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4936,7 +4942,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4944,7 +4950,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4952,7 +4958,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4960,7 +4966,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4968,7 +4974,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4976,7 +4982,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4984,7 +4990,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4992,7 +4998,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -5000,7 +5006,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -5008,7 +5014,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -5016,7 +5022,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -5024,7 +5030,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -5032,7 +5038,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -5040,7 +5046,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -5048,7 +5054,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -5056,7 +5062,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -5064,7 +5070,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -5072,7 +5078,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -5080,7 +5086,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -5088,7 +5094,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -5096,7 +5102,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -5104,7 +5110,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -5112,7 +5118,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -5120,7 +5126,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -5128,7 +5134,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -5136,7 +5142,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5144,7 +5150,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5152,7 +5158,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5160,7 +5166,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5168,7 +5174,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5176,7 +5182,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5184,7 +5190,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5192,7 +5198,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5200,7 +5206,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5208,7 +5214,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5216,7 +5222,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5224,7 +5230,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5232,7 +5238,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5240,7 +5246,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5248,7 +5254,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5256,7 +5262,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5264,7 +5270,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5272,7 +5278,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5280,7 +5286,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5288,7 +5294,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5296,7 +5302,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5316,14 +5322,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5334,7 +5340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5345,7 +5351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5364,9 +5370,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5389,7 +5395,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5412,7 +5418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5432,10 +5438,10 @@
         <v>500</v>
       </c>
       <c r="G3" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -5455,7 +5461,7 @@
         <v>500</v>
       </c>
       <c r="G4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5465,10 +5471,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5490,11 +5496,14 @@
       <c r="G1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="70" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="71" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5516,11 +5525,14 @@
       <c r="G2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="70" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5542,8 +5554,11 @@
       <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="H3" s="3">
-        <v>1000</v>
+      <c r="H3" s="72">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="75">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5554,16 +5569,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3F3123-4F4E-48AE-BFD8-F7DBC7028FBB}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5580,7 +5595,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -5597,7 +5612,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="72">
         <v>1</v>
       </c>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782BC8F8-F3CE-40CE-B3EA-BFA125998358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC12E43-E55E-4906-AF41-ACF12EAF6AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="203">
   <si>
     <t>id</t>
   </si>
@@ -228,13 +228,7 @@
     <t>0.95</t>
   </si>
   <si>
-    <t>LH518B_2</t>
-  </si>
-  <si>
-    <t>LH518B_3</t>
-  </si>
-  <si>
-    <t>LH518B_4</t>
+    <t>swap_time</t>
   </si>
   <si>
     <t>LH518B</t>
@@ -531,6 +525,9 @@
     <t>USD</t>
   </si>
   <si>
+    <t>h</t>
+  </si>
+  <si>
     <t>station_1</t>
   </si>
   <si>
@@ -555,6 +552,15 @@
     <t>p_max_ssee</t>
   </si>
   <si>
+    <t>battery_cost</t>
+  </si>
+  <si>
+    <t>charge_time</t>
+  </si>
+  <si>
+    <t>Battery_swap</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -603,21 +609,27 @@
     <t>Bess</t>
   </si>
   <si>
-    <t>electric</t>
-  </si>
-  <si>
     <t>c_fixed</t>
   </si>
   <si>
     <t>c_bays</t>
   </si>
   <si>
+    <t>c_crane</t>
+  </si>
+  <si>
     <t>c_charger_space</t>
   </si>
   <si>
+    <t>c_battery_space</t>
+  </si>
+  <si>
     <t>max_bays</t>
   </si>
   <si>
+    <t>max_batteries_per_bay</t>
+  </si>
+  <si>
     <t>max_chargers_per_bay</t>
   </si>
   <si>
@@ -636,7 +648,7 @@
     <t>%</t>
   </si>
   <si>
-    <t>0.1</t>
+    <t>h_max</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1010,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1204,17 +1216,20 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1522,38 +1537,37 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1641,8 +1655,14 @@
       <c r="AC1" s="27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD1" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE1" s="27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1730,25 +1750,31 @@
       <c r="AC2" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD2" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE2" s="27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
-        <v>160</v>
+      <c r="C3" s="38" t="s">
+        <v>158</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G3" s="9">
         <v>18</v>
@@ -1819,273 +1845,25 @@
       <c r="AC3" s="34" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="31">
-        <v>2</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="9">
-        <v>18</v>
-      </c>
-      <c r="H4" s="22">
-        <v>0.84</v>
-      </c>
-      <c r="I4" s="9">
-        <v>20</v>
-      </c>
-      <c r="J4" s="9">
-        <v>20</v>
-      </c>
-      <c r="K4" s="9">
-        <v>52</v>
-      </c>
-      <c r="L4" s="9">
-        <v>540</v>
-      </c>
-      <c r="M4" s="22">
-        <v>6.26</v>
-      </c>
-      <c r="N4" s="35">
-        <v>-1</v>
-      </c>
-      <c r="O4" s="35">
-        <v>-1</v>
-      </c>
-      <c r="P4" s="35">
-        <v>-1</v>
-      </c>
-      <c r="Q4" s="35">
-        <v>-1</v>
-      </c>
-      <c r="R4" s="22">
-        <v>0.85</v>
-      </c>
-      <c r="S4" s="26">
-        <v>0.92</v>
-      </c>
-      <c r="T4" s="28">
-        <v>16.2</v>
-      </c>
-      <c r="U4" s="28">
-        <v>0.47</v>
-      </c>
-      <c r="V4" s="34">
-        <v>100</v>
-      </c>
-      <c r="W4" s="34">
-        <v>4</v>
-      </c>
-      <c r="X4" s="34">
-        <v>360</v>
-      </c>
-      <c r="Y4" s="34">
-        <v>4</v>
-      </c>
-      <c r="Z4" s="34">
-        <v>353</v>
-      </c>
-      <c r="AA4" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB4" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC4" s="34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="31">
-        <v>3</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="9">
-        <v>18</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0.84</v>
-      </c>
-      <c r="I5" s="9">
-        <v>20</v>
-      </c>
-      <c r="J5" s="9">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9">
-        <v>52</v>
-      </c>
-      <c r="L5" s="9">
-        <v>540</v>
-      </c>
-      <c r="M5" s="22">
-        <v>6.26</v>
-      </c>
-      <c r="N5" s="35">
-        <v>-1</v>
-      </c>
-      <c r="O5" s="35">
-        <v>-1</v>
-      </c>
-      <c r="P5" s="35">
-        <v>-1</v>
-      </c>
-      <c r="Q5" s="35">
-        <v>-1</v>
-      </c>
-      <c r="R5" s="22">
-        <v>0.85</v>
-      </c>
-      <c r="S5" s="26">
-        <v>0.92</v>
-      </c>
-      <c r="T5" s="28">
-        <v>16.2</v>
-      </c>
-      <c r="U5" s="28">
-        <v>0.47</v>
-      </c>
-      <c r="V5" s="34">
-        <v>100</v>
-      </c>
-      <c r="W5" s="34">
-        <v>4</v>
-      </c>
-      <c r="X5" s="34">
-        <v>360</v>
-      </c>
-      <c r="Y5" s="34">
-        <v>4</v>
-      </c>
-      <c r="Z5" s="34">
-        <v>353</v>
-      </c>
-      <c r="AA5" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB5" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" s="34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
-        <v>4</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="9">
-        <v>18</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0.84</v>
-      </c>
-      <c r="I6" s="9">
-        <v>20</v>
-      </c>
-      <c r="J6" s="9">
-        <v>20</v>
-      </c>
-      <c r="K6" s="9">
-        <v>52</v>
-      </c>
-      <c r="L6" s="9">
-        <v>540</v>
-      </c>
-      <c r="M6" s="22">
-        <v>6.26</v>
-      </c>
-      <c r="N6" s="35">
-        <v>-1</v>
-      </c>
-      <c r="O6" s="35">
-        <v>-1</v>
-      </c>
-      <c r="P6" s="35">
-        <v>-1</v>
-      </c>
-      <c r="Q6" s="35">
-        <v>-1</v>
-      </c>
-      <c r="R6" s="22">
-        <v>0.85</v>
-      </c>
-      <c r="S6" s="26">
-        <v>0.92</v>
-      </c>
-      <c r="T6" s="28">
-        <v>16.2</v>
-      </c>
-      <c r="U6" s="28">
-        <v>0.47</v>
-      </c>
-      <c r="V6" s="34">
-        <v>100</v>
-      </c>
-      <c r="W6" s="34">
-        <v>4</v>
-      </c>
-      <c r="X6" s="34">
-        <v>360</v>
-      </c>
-      <c r="Y6" s="34">
-        <v>4</v>
-      </c>
-      <c r="Z6" s="34">
-        <v>353</v>
-      </c>
-      <c r="AA6" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB6" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC6" s="34" t="s">
-        <v>61</v>
-      </c>
+      <c r="AD3" s="34">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AE3" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2095,91 +1873,106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
-        <v>1</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>163</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="34">
+        <v>35722</v>
       </c>
       <c r="C3" s="34">
-        <v>35722</v>
+        <v>38221</v>
       </c>
       <c r="D3" s="34">
-        <v>38221</v>
+        <v>16752</v>
       </c>
       <c r="E3" s="34">
         <v>5733</v>
       </c>
       <c r="F3" s="34">
+        <v>4389</v>
+      </c>
+      <c r="G3" s="34">
         <v>2</v>
       </c>
-      <c r="G3" s="34">
-        <v>1</v>
-      </c>
       <c r="H3" s="34">
+        <v>2</v>
+      </c>
+      <c r="I3" s="34">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34">
         <v>1500</v>
       </c>
     </row>
@@ -2191,30 +1984,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="D1" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="F1" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="27" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
@@ -2222,7 +2021,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>34</v>
@@ -2233,13 +2032,19 @@
       <c r="F2" s="27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>1</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="34">
         <v>42071</v>
@@ -2252,6 +2057,12 @@
       </c>
       <c r="F3" s="34">
         <v>5000</v>
+      </c>
+      <c r="G3" s="34">
+        <v>79000</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2265,17 +2076,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2301,7 +2112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2327,12 +2138,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>0</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>6</v>
@@ -2353,12 +2164,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>6</v>
@@ -2379,12 +2190,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" s="60" t="s">
         <v>6</v>
@@ -2405,12 +2216,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" s="60" t="s">
         <v>6</v>
@@ -2431,12 +2242,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="60" t="s">
         <v>6</v>
@@ -2457,12 +2268,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" s="60" t="s">
         <v>6</v>
@@ -2483,12 +2294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>6</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>6</v>
@@ -2509,12 +2320,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="60" t="s">
         <v>6</v>
@@ -2535,12 +2346,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="60" t="s">
         <v>6</v>
@@ -2561,12 +2372,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>9</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>6</v>
@@ -2587,12 +2398,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="60" t="s">
         <v>6</v>
@@ -2613,12 +2424,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C14" s="60" t="s">
         <v>6</v>
@@ -2639,12 +2450,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C15" s="60" t="s">
         <v>6</v>
@@ -2665,12 +2476,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>13</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C16" s="60" t="s">
         <v>6</v>
@@ -2691,12 +2502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C17" s="60" t="s">
         <v>6</v>
@@ -2717,12 +2528,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C18" s="60" t="s">
         <v>6</v>
@@ -2743,12 +2554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>16</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="60" t="s">
         <v>6</v>
@@ -2769,12 +2580,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="60" t="s">
         <v>6</v>
@@ -2795,12 +2606,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C21" s="60" t="s">
         <v>6</v>
@@ -2821,12 +2632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>19</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C22" s="60" t="s">
         <v>6</v>
@@ -2847,12 +2658,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C23" s="60" t="s">
         <v>6</v>
@@ -2873,12 +2684,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C24" s="60" t="s">
         <v>6</v>
@@ -2899,12 +2710,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C25" s="60" t="s">
         <v>6</v>
@@ -2925,12 +2736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>23</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="60" t="s">
         <v>13</v>
@@ -2951,12 +2762,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" s="60" t="s">
         <v>13</v>
@@ -2977,12 +2788,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>25</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" s="60" t="s">
         <v>13</v>
@@ -3003,12 +2814,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" s="60" t="s">
         <v>13</v>
@@ -3029,12 +2840,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C30" s="60" t="s">
         <v>13</v>
@@ -3055,12 +2866,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>28</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="60" t="s">
         <v>13</v>
@@ -3081,12 +2892,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="60" t="s">
         <v>13</v>
@@ -3107,12 +2918,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" s="60" t="s">
         <v>13</v>
@@ -3133,12 +2944,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>31</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="60" t="s">
         <v>13</v>
@@ -3159,12 +2970,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="60" t="s">
         <v>13</v>
@@ -3185,12 +2996,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="60" t="s">
         <v>13</v>
@@ -3211,12 +3022,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52">
         <v>34</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C37" s="60" t="s">
         <v>13</v>
@@ -3237,12 +3048,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C38" s="60" t="s">
         <v>13</v>
@@ -3263,12 +3074,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="60" t="s">
         <v>13</v>
@@ -3289,12 +3100,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C40" s="60" t="s">
         <v>13</v>
@@ -3315,12 +3126,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>38</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C41" s="60" t="s">
         <v>13</v>
@@ -3341,12 +3152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C42" s="60" t="s">
         <v>13</v>
@@ -3367,12 +3178,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C43" s="60" t="s">
         <v>13</v>
@@ -3393,12 +3204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C44" s="60" t="s">
         <v>13</v>
@@ -3419,12 +3230,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C45" s="60" t="s">
         <v>13</v>
@@ -3445,12 +3256,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C46" s="60" t="s">
         <v>13</v>
@@ -3471,12 +3282,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" s="60" t="s">
         <v>13</v>
@@ -3497,12 +3308,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C48" s="60" t="s">
         <v>13</v>
@@ -3523,12 +3334,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" s="60" t="s">
         <v>13</v>
@@ -3549,12 +3360,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C50" s="60" t="s">
         <v>14</v>
@@ -3575,12 +3386,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C51" s="60" t="s">
         <v>14</v>
@@ -3601,12 +3412,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C52" s="60" t="s">
         <v>14</v>
@@ -3627,12 +3438,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C53" s="60" t="s">
         <v>14</v>
@@ -3653,12 +3464,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C54" s="60" t="s">
         <v>14</v>
@@ -3679,12 +3490,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
       <c r="B55" s="48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C55" s="60" t="s">
         <v>14</v>
@@ -3705,12 +3516,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" s="60" t="s">
         <v>14</v>
@@ -3731,12 +3542,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C57" s="60" t="s">
         <v>14</v>
@@ -3757,12 +3568,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
       <c r="B58" s="48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58" s="60" t="s">
         <v>14</v>
@@ -3783,12 +3594,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C59" s="60" t="s">
         <v>14</v>
@@ -3809,12 +3620,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C60" s="60" t="s">
         <v>14</v>
@@ -3835,12 +3646,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C61" s="60" t="s">
         <v>14</v>
@@ -3861,12 +3672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C62" s="60" t="s">
         <v>14</v>
@@ -3887,12 +3698,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C63" s="60" t="s">
         <v>14</v>
@@ -3913,12 +3724,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C64" s="60" t="s">
         <v>14</v>
@@ -3939,12 +3750,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
       <c r="B65" s="48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C65" s="60" t="s">
         <v>14</v>
@@ -3965,12 +3776,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
       <c r="B66" s="48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C66" s="60" t="s">
         <v>14</v>
@@ -3991,12 +3802,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C67" s="60" t="s">
         <v>14</v>
@@ -4017,12 +3828,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
       <c r="B68" s="48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C68" s="60" t="s">
         <v>14</v>
@@ -4043,12 +3854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C69" s="60" t="s">
         <v>14</v>
@@ -4069,12 +3880,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="60" t="s">
         <v>14</v>
@@ -4095,12 +3906,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C71" s="60" t="s">
         <v>14</v>
@@ -4121,12 +3932,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C72" s="60" t="s">
         <v>14</v>
@@ -4147,12 +3958,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C73" s="60" t="s">
         <v>14</v>
@@ -4173,12 +3984,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C74" s="60" t="s">
         <v>15</v>
@@ -4199,12 +4010,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C75" s="60" t="s">
         <v>15</v>
@@ -4225,12 +4036,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C76" s="60" t="s">
         <v>15</v>
@@ -4251,12 +4062,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C77" s="60" t="s">
         <v>15</v>
@@ -4277,12 +4088,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C78" s="60" t="s">
         <v>15</v>
@@ -4303,12 +4114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C79" s="60" t="s">
         <v>15</v>
@@ -4329,12 +4140,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
       <c r="B80" s="48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C80" s="60" t="s">
         <v>15</v>
@@ -4355,12 +4166,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
       <c r="B81" s="48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C81" s="60" t="s">
         <v>15</v>
@@ -4381,12 +4192,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C82" s="60" t="s">
         <v>15</v>
@@ -4407,12 +4218,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
       <c r="B83" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C83" s="60" t="s">
         <v>15</v>
@@ -4433,12 +4244,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C84" s="60" t="s">
         <v>15</v>
@@ -4459,12 +4270,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
       <c r="B85" s="48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C85" s="60" t="s">
         <v>15</v>
@@ -4485,12 +4296,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
       <c r="B86" s="48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="60" t="s">
         <v>15</v>
@@ -4511,12 +4322,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C87" s="60" t="s">
         <v>15</v>
@@ -4537,12 +4348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
       <c r="B88" s="48" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C88" s="60" t="s">
         <v>15</v>
@@ -4563,12 +4374,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
       <c r="B89" s="48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C89" s="60" t="s">
         <v>15</v>
@@ -4589,12 +4400,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
       <c r="B90" s="48" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C90" s="60" t="s">
         <v>15</v>
@@ -4615,12 +4426,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
       <c r="B91" s="48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C91" s="60" t="s">
         <v>15</v>
@@ -4641,12 +4452,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
       <c r="B92" s="48" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C92" s="60" t="s">
         <v>15</v>
@@ -4667,12 +4478,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
       <c r="B93" s="48" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C93" s="60" t="s">
         <v>15</v>
@@ -4693,12 +4504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
       <c r="B94" s="48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C94" s="60" t="s">
         <v>15</v>
@@ -4719,12 +4530,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
       <c r="B95" s="48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C95" s="60" t="s">
         <v>15</v>
@@ -4745,12 +4556,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
       <c r="B96" s="48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C96" s="60" t="s">
         <v>15</v>
@@ -4771,16 +4582,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="53"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4788,7 +4593,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4796,7 +4601,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4804,7 +4609,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4812,7 +4617,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4820,7 +4625,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4828,7 +4633,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4836,7 +4641,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4844,7 +4649,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4852,7 +4657,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4860,7 +4665,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4868,7 +4673,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4876,7 +4681,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4884,7 +4689,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4892,7 +4697,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4900,7 +4705,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4908,7 +4713,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -4916,7 +4721,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -4924,7 +4729,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -4932,7 +4737,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -4940,7 +4745,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -4948,7 +4753,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -4956,7 +4761,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -4964,7 +4769,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -4972,7 +4777,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -4980,7 +4785,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -4988,7 +4793,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -4996,7 +4801,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -5004,7 +4809,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -5012,7 +4817,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -5020,7 +4825,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -5028,7 +4833,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -5036,7 +4841,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -5044,7 +4849,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -5052,7 +4857,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5060,7 +4865,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5068,7 +4873,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5076,7 +4881,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5084,7 +4889,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5092,7 +4897,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5100,7 +4905,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5108,7 +4913,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5116,7 +4921,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5124,7 +4929,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5132,7 +4937,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5140,7 +4945,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5148,7 +4953,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5156,7 +4961,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5164,7 +4969,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5172,7 +4977,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5180,7 +4985,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5188,7 +4993,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5196,7 +5001,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5204,7 +5009,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5212,7 +5017,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5232,14 +5037,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5250,7 +5055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5261,7 +5066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5280,9 +5085,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5290,22 +5095,22 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5316,10 +5121,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -5328,15 +5133,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3">
         <v>30.8</v>
@@ -5348,18 +5153,18 @@
         <v>500</v>
       </c>
       <c r="G3" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D4" s="3">
         <v>119</v>
@@ -5371,7 +5176,7 @@
         <v>500</v>
       </c>
       <c r="G4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5381,13 +5186,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5395,25 +5197,28 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="H1" s="70" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5421,10 +5226,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -5435,16 +5240,19 @@
       <c r="G2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="70" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C3" s="4">
         <v>18308</v>
@@ -5461,8 +5269,11 @@
       <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="H3" s="3">
-        <v>1000</v>
+      <c r="H3" s="72">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="75">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5471,34 +5282,35 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB361D3-2C0F-481F-8505-844CB2F9BDD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3F3123-4F4E-48AE-BFD8-F7DBC7028FBB}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="72" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -5506,30 +5318,30 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="72" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="73">
+        <v>160</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="72">
         <v>1</v>
       </c>
       <c r="B3" s="34">
         <v>2.3532999999999998E-2</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="73">
         <v>299000</v>
       </c>
-      <c r="D3" s="71">
+      <c r="D3" s="74">
         <v>0.8</v>
       </c>
-      <c r="E3" s="34" t="s">
-        <v>198</v>
+      <c r="E3" s="34">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50151E09-B5F2-472C-BEDF-F8141D06AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F58600-7455-410F-807F-A0886F07003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -5438,7 +5438,7 @@
         <v>500</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -5461,7 +5461,7 @@
         <v>500</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5558,7 +5558,7 @@
         <v>1000</v>
       </c>
       <c r="I3" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\320kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494F878C-4ED5-4E81-B5F5-ABBB7D2F2A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC280CF-3E6F-485E-A98B-73E8EA598A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -427,6 +427,237 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>C0554</t>
+  </si>
+  <si>
+    <t>street_2</t>
+  </si>
+  <si>
+    <t>C0555</t>
+  </si>
+  <si>
+    <t>C0556</t>
+  </si>
+  <si>
+    <t>C0557</t>
+  </si>
+  <si>
+    <t>C0558</t>
+  </si>
+  <si>
+    <t>C0559</t>
+  </si>
+  <si>
+    <t>C0560</t>
+  </si>
+  <si>
+    <t>C0561</t>
+  </si>
+  <si>
+    <t>C0562</t>
+  </si>
+  <si>
+    <t>C0563</t>
+  </si>
+  <si>
+    <t>C0564</t>
+  </si>
+  <si>
+    <t>C0565</t>
+  </si>
+  <si>
+    <t>C0527</t>
+  </si>
+  <si>
+    <t>C0528</t>
+  </si>
+  <si>
+    <t>C0529</t>
+  </si>
+  <si>
+    <t>C0530</t>
+  </si>
+  <si>
+    <t>C0531</t>
+  </si>
+  <si>
+    <t>C0532</t>
+  </si>
+  <si>
+    <t>C0533</t>
+  </si>
+  <si>
+    <t>C0534</t>
+  </si>
+  <si>
+    <t>C0535</t>
+  </si>
+  <si>
+    <t>C0536</t>
+  </si>
+  <si>
+    <t>C0537</t>
+  </si>
+  <si>
+    <t>C0538</t>
+  </si>
+  <si>
+    <t>C0499</t>
+  </si>
+  <si>
+    <t>street_3</t>
+  </si>
+  <si>
+    <t>C0500</t>
+  </si>
+  <si>
+    <t>C0501</t>
+  </si>
+  <si>
+    <t>C0502</t>
+  </si>
+  <si>
+    <t>C0503</t>
+  </si>
+  <si>
+    <t>C0504</t>
+  </si>
+  <si>
+    <t>C0505</t>
+  </si>
+  <si>
+    <t>C0506</t>
+  </si>
+  <si>
+    <t>C0507</t>
+  </si>
+  <si>
+    <t>C0508</t>
+  </si>
+  <si>
+    <t>C0509</t>
+  </si>
+  <si>
+    <t>C0510</t>
+  </si>
+  <si>
+    <t>C0472</t>
+  </si>
+  <si>
+    <t>C0473</t>
+  </si>
+  <si>
+    <t>C0474</t>
+  </si>
+  <si>
+    <t>C0475</t>
+  </si>
+  <si>
+    <t>C0476</t>
+  </si>
+  <si>
+    <t>C0477</t>
+  </si>
+  <si>
+    <t>C0478</t>
+  </si>
+  <si>
+    <t>C0479</t>
+  </si>
+  <si>
+    <t>C0480</t>
+  </si>
+  <si>
+    <t>C0481</t>
+  </si>
+  <si>
+    <t>C0482</t>
+  </si>
+  <si>
+    <t>C0483</t>
+  </si>
+  <si>
+    <t>C0440</t>
+  </si>
+  <si>
+    <t>street_4</t>
+  </si>
+  <si>
+    <t>C0441</t>
+  </si>
+  <si>
+    <t>C0442</t>
+  </si>
+  <si>
+    <t>C0443</t>
+  </si>
+  <si>
+    <t>C0444</t>
+  </si>
+  <si>
+    <t>C0445</t>
+  </si>
+  <si>
+    <t>C0446</t>
+  </si>
+  <si>
+    <t>C0447</t>
+  </si>
+  <si>
+    <t>C0448</t>
+  </si>
+  <si>
+    <t>C0449</t>
+  </si>
+  <si>
+    <t>C0450</t>
+  </si>
+  <si>
+    <t>C0451</t>
+  </si>
+  <si>
+    <t>C0409</t>
+  </si>
+  <si>
+    <t>C0410</t>
+  </si>
+  <si>
+    <t>C0411</t>
+  </si>
+  <si>
+    <t>C0412</t>
+  </si>
+  <si>
+    <t>C0413</t>
+  </si>
+  <si>
+    <t>C0414</t>
+  </si>
+  <si>
+    <t>C0415</t>
+  </si>
+  <si>
+    <t>C0416</t>
+  </si>
+  <si>
+    <t>C0417</t>
+  </si>
+  <si>
+    <t>C0418</t>
+  </si>
+  <si>
+    <t>C0419</t>
+  </si>
+  <si>
+    <t>LH518B_2</t>
+  </si>
+  <si>
+    <t>LH518B_3</t>
+  </si>
+  <si>
+    <t>LH518B_4</t>
   </si>
 </sst>
 </file>
@@ -753,7 +984,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -787,9 +1018,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -838,12 +1066,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -952,6 +1174,12 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1260,248 +1488,248 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="22" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" style="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.85546875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="T1" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="27" t="s">
+      <c r="U1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="V1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="W1" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="X1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="27" t="s">
+      <c r="Y1" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="Z1" s="27" t="s">
+      <c r="Z1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AA1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AB1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="27" t="s">
+      <c r="AC1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AD1" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="O2" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="P2" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="W2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="X2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Y2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="Z2" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AA2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AB2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="27" t="s">
+      <c r="AC2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AD2" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AE2" s="26" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31">
+    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="67">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>60</v>
       </c>
       <c r="G3" s="9">
         <v>18</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>0.84</v>
       </c>
       <c r="I3" s="9">
@@ -1516,73 +1744,355 @@
       <c r="L3" s="9">
         <v>540</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="21">
         <v>6.26</v>
       </c>
-      <c r="N3" s="35">
+      <c r="N3" s="32">
         <v>-1</v>
       </c>
-      <c r="O3" s="35">
+      <c r="O3" s="32">
         <v>-1</v>
       </c>
-      <c r="P3" s="35">
+      <c r="P3" s="32">
         <v>-1</v>
       </c>
-      <c r="Q3" s="35">
+      <c r="Q3" s="32">
         <v>-1</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="21">
         <v>0.85</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="25">
         <v>0.92</v>
       </c>
-      <c r="T3" s="28">
+      <c r="T3" s="27">
         <v>16.2</v>
       </c>
-      <c r="U3" s="28">
+      <c r="U3" s="27">
         <v>0.47</v>
       </c>
-      <c r="V3" s="34">
+      <c r="V3" s="31">
         <v>100</v>
       </c>
-      <c r="W3" s="34">
+      <c r="W3" s="31">
         <v>4</v>
       </c>
-      <c r="X3" s="34">
+      <c r="X3" s="31">
         <v>360</v>
       </c>
-      <c r="Y3" s="34">
+      <c r="Y3" s="31">
         <v>4</v>
       </c>
-      <c r="Z3" s="34">
+      <c r="Z3" s="31">
         <v>353</v>
       </c>
-      <c r="AA3" s="34" t="s">
+      <c r="AA3" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="AB3" s="34" t="s">
+      <c r="AB3" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" s="34" t="s">
+      <c r="AC3" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="34">
+      <c r="AD3" s="31">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="AE3" s="34">
+      <c r="AE3" s="31">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="67">
+        <v>2</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="9">
+        <v>18</v>
+      </c>
+      <c r="H4" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="I4" s="9">
+        <v>20</v>
+      </c>
+      <c r="J4" s="9">
+        <v>20</v>
+      </c>
+      <c r="K4" s="9">
+        <v>52</v>
+      </c>
+      <c r="L4" s="9">
+        <v>540</v>
+      </c>
+      <c r="M4" s="21">
+        <v>6.26</v>
+      </c>
+      <c r="N4" s="32">
+        <v>-1</v>
+      </c>
+      <c r="O4" s="32">
+        <v>-1</v>
+      </c>
+      <c r="P4" s="32">
+        <v>-1</v>
+      </c>
+      <c r="Q4" s="32">
+        <v>-1</v>
+      </c>
+      <c r="R4" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="S4" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="T4" s="27">
+        <v>16.2</v>
+      </c>
+      <c r="U4" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="V4" s="31">
+        <v>100</v>
+      </c>
+      <c r="W4" s="31">
+        <v>4</v>
+      </c>
+      <c r="X4" s="31">
+        <v>360</v>
+      </c>
+      <c r="Y4" s="31">
+        <v>4</v>
+      </c>
+      <c r="Z4" s="31">
+        <v>353</v>
+      </c>
+      <c r="AA4" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD4" s="31">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AE4" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="67">
+        <v>3</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="9">
+        <v>18</v>
+      </c>
+      <c r="H5" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="I5" s="9">
+        <v>20</v>
+      </c>
+      <c r="J5" s="9">
+        <v>20</v>
+      </c>
+      <c r="K5" s="9">
+        <v>52</v>
+      </c>
+      <c r="L5" s="9">
+        <v>540</v>
+      </c>
+      <c r="M5" s="21">
+        <v>6.26</v>
+      </c>
+      <c r="N5" s="32">
+        <v>-1</v>
+      </c>
+      <c r="O5" s="32">
+        <v>-1</v>
+      </c>
+      <c r="P5" s="32">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="32">
+        <v>-1</v>
+      </c>
+      <c r="R5" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="S5" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="T5" s="27">
+        <v>16.2</v>
+      </c>
+      <c r="U5" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="V5" s="31">
+        <v>100</v>
+      </c>
+      <c r="W5" s="31">
+        <v>4</v>
+      </c>
+      <c r="X5" s="31">
+        <v>360</v>
+      </c>
+      <c r="Y5" s="31">
+        <v>4</v>
+      </c>
+      <c r="Z5" s="31">
+        <v>353</v>
+      </c>
+      <c r="AA5" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB5" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC5" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD5" s="31">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AE5" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67">
+        <v>4</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="9">
+        <v>18</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="I6" s="9">
+        <v>20</v>
+      </c>
+      <c r="J6" s="9">
+        <v>20</v>
+      </c>
+      <c r="K6" s="9">
+        <v>52</v>
+      </c>
+      <c r="L6" s="9">
+        <v>540</v>
+      </c>
+      <c r="M6" s="21">
+        <v>6.26</v>
+      </c>
+      <c r="N6" s="32">
+        <v>-1</v>
+      </c>
+      <c r="O6" s="32">
+        <v>-1</v>
+      </c>
+      <c r="P6" s="32">
+        <v>-1</v>
+      </c>
+      <c r="Q6" s="32">
+        <v>-1</v>
+      </c>
+      <c r="R6" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="S6" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="T6" s="27">
+        <v>16.2</v>
+      </c>
+      <c r="U6" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="V6" s="31">
+        <v>100</v>
+      </c>
+      <c r="W6" s="31">
+        <v>4</v>
+      </c>
+      <c r="X6" s="31">
+        <v>360</v>
+      </c>
+      <c r="Y6" s="31">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="31">
+        <v>353</v>
+      </c>
+      <c r="AA6" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB6" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC6" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD6" s="31">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AE6" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="Y7"/>
       <c r="Z7"/>
       <c r="AA7"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="Y8"/>
       <c r="Z8"/>
       <c r="AA8"/>
@@ -1596,105 +2106,105 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="26" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="31">
         <v>35722</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="31">
         <v>38221</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="31">
         <v>16752</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="31">
         <v>5733</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="31">
         <v>4389</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="31">
         <v>2</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="31">
         <v>2</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="31">
         <v>2</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J3" s="31">
         <v>1500</v>
       </c>
     </row>
@@ -1707,83 +2217,83 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="34">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="31">
         <v>42071</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="31">
         <v>320</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="31">
         <v>1</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="31">
         <v>5000</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="31">
         <v>79000</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="31" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1798,33 +2308,33 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.109375" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="57" t="s">
         <v>55</v>
       </c>
       <c r="G1" s="7" t="s">
@@ -1834,758 +2344,2477 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="38" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49">
-        <v>0</v>
-      </c>
-      <c r="B3" s="45" t="s">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46">
+        <v>0</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="62">
-        <v>61.592606358896269</v>
-      </c>
-      <c r="F3" s="62">
-        <v>61.592606358896269</v>
-      </c>
-      <c r="G3" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H3" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50">
+      <c r="D3" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="59">
+        <v>61.59</v>
+      </c>
+      <c r="F3" s="59">
+        <v>61.59</v>
+      </c>
+      <c r="G3" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="47">
         <v>1</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="62">
-        <v>83.592606358896262</v>
-      </c>
-      <c r="F4" s="62">
-        <v>83.592606358896262</v>
-      </c>
-      <c r="G4" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H4" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="50">
+      <c r="D4" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="59">
+        <v>83.59</v>
+      </c>
+      <c r="F4" s="59">
+        <v>83.59</v>
+      </c>
+      <c r="G4" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
         <v>2</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="62">
-        <v>105.5926063588963</v>
-      </c>
-      <c r="F5" s="62">
-        <v>105.5926063588963</v>
-      </c>
-      <c r="G5" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49">
+      <c r="D5" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="59">
+        <v>105.59</v>
+      </c>
+      <c r="F5" s="59">
+        <v>105.59</v>
+      </c>
+      <c r="G5" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="46">
         <v>3</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="62">
-        <v>127.5926063588963</v>
-      </c>
-      <c r="F6" s="62">
-        <v>127.5926063588963</v>
-      </c>
-      <c r="G6" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50">
+      <c r="D6" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="59">
+        <v>127.59</v>
+      </c>
+      <c r="F6" s="59">
+        <v>127.59</v>
+      </c>
+      <c r="G6" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47">
         <v>4</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="62">
-        <v>149.59260635889629</v>
-      </c>
-      <c r="F7" s="62">
-        <v>149.59260635889629</v>
-      </c>
-      <c r="G7" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H7" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50">
-        <v>5</v>
-      </c>
-      <c r="B8" s="45" t="s">
+      <c r="D7" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="59">
+        <v>149.59</v>
+      </c>
+      <c r="F7" s="59">
+        <v>149.59</v>
+      </c>
+      <c r="G7" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="47">
+        <v>5</v>
+      </c>
+      <c r="B8" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="62">
-        <v>171.59260635889629</v>
-      </c>
-      <c r="F8" s="62">
-        <v>171.59260635889629</v>
-      </c>
-      <c r="G8" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H8" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49">
+      <c r="D8" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="59">
+        <v>171.59</v>
+      </c>
+      <c r="F8" s="59">
+        <v>171.59</v>
+      </c>
+      <c r="G8" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46">
         <v>6</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="62">
-        <v>193.59260635889629</v>
-      </c>
-      <c r="F9" s="62">
-        <v>193.59260635889629</v>
-      </c>
-      <c r="G9" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H9" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50">
+      <c r="D9" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="59">
+        <v>193.59</v>
+      </c>
+      <c r="F9" s="59">
+        <v>193.59</v>
+      </c>
+      <c r="G9" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
         <v>7</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="62">
-        <v>180.90167233126809</v>
-      </c>
-      <c r="F10" s="62">
-        <v>180.90167233126809</v>
-      </c>
-      <c r="G10" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H10" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50">
+      <c r="D10" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="59">
+        <v>180.9</v>
+      </c>
+      <c r="F10" s="59">
+        <v>180.9</v>
+      </c>
+      <c r="G10" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
         <v>8</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="62">
-        <v>158.90167233126809</v>
-      </c>
-      <c r="F11" s="62">
-        <v>158.90167233126809</v>
-      </c>
-      <c r="G11" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H11" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49">
+      <c r="D11" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="59">
+        <v>158.9</v>
+      </c>
+      <c r="F11" s="59">
+        <v>158.9</v>
+      </c>
+      <c r="G11" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="46">
         <v>9</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="62">
-        <v>136.90167233126809</v>
-      </c>
-      <c r="F12" s="62">
-        <v>136.90167233126809</v>
-      </c>
-      <c r="G12" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H12" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50">
+      <c r="D12" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="59">
+        <v>136.9</v>
+      </c>
+      <c r="F12" s="59">
+        <v>136.9</v>
+      </c>
+      <c r="G12" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
         <v>10</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="62">
-        <v>114.901672331268</v>
-      </c>
-      <c r="F13" s="62">
-        <v>114.901672331268</v>
-      </c>
-      <c r="G13" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H13" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50">
+      <c r="D13" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="59">
+        <v>114.9</v>
+      </c>
+      <c r="F13" s="59">
+        <v>114.9</v>
+      </c>
+      <c r="G13" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47">
         <v>11</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="63">
-        <v>68.033612034816727</v>
-      </c>
-      <c r="F14" s="63">
-        <v>68.033612034816727</v>
-      </c>
-      <c r="G14" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H14" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="50">
+      <c r="D14" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="60">
+        <v>68.03</v>
+      </c>
+      <c r="F14" s="60">
+        <v>68.03</v>
+      </c>
+      <c r="G14" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47">
         <v>12</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="63">
-        <v>90.033612034816727</v>
-      </c>
-      <c r="F15" s="63">
-        <v>90.033612034816727</v>
-      </c>
-      <c r="G15" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H15" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="49">
+      <c r="D15" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="60">
+        <v>90.03</v>
+      </c>
+      <c r="F15" s="60">
+        <v>90.03</v>
+      </c>
+      <c r="G15" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="46">
         <v>13</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="63">
-        <v>112.0336120348167</v>
-      </c>
-      <c r="F16" s="63">
-        <v>112.0336120348167</v>
-      </c>
-      <c r="G16" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H16" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50">
+      <c r="D16" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="60">
+        <v>112.03</v>
+      </c>
+      <c r="F16" s="60">
+        <v>112.03</v>
+      </c>
+      <c r="G16" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47">
         <v>14</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="63">
-        <v>134.03361203481671</v>
-      </c>
-      <c r="F17" s="63">
-        <v>134.03361203481671</v>
-      </c>
-      <c r="G17" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H17" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50">
+      <c r="D17" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="60">
+        <v>134.03</v>
+      </c>
+      <c r="F17" s="60">
+        <v>134.03</v>
+      </c>
+      <c r="G17" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="47">
         <v>15</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="63">
-        <v>156.03361203481671</v>
-      </c>
-      <c r="F18" s="63">
-        <v>156.03361203481671</v>
-      </c>
-      <c r="G18" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="49">
+      <c r="D18" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="60">
+        <v>156.03</v>
+      </c>
+      <c r="F18" s="60">
+        <v>156.03</v>
+      </c>
+      <c r="G18" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="46">
         <v>16</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="63">
-        <v>178.03361203481671</v>
-      </c>
-      <c r="F19" s="63">
-        <v>178.03361203481671</v>
-      </c>
-      <c r="G19" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H19" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50">
+      <c r="D19" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="60">
+        <v>178.03</v>
+      </c>
+      <c r="F19" s="60">
+        <v>178.03</v>
+      </c>
+      <c r="G19" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="47">
         <v>17</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="63">
-        <v>194.74680630994109</v>
-      </c>
-      <c r="F20" s="63">
-        <v>194.74680630994109</v>
-      </c>
-      <c r="G20" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H20" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50">
+      <c r="D20" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="60">
+        <v>194.75</v>
+      </c>
+      <c r="F20" s="60">
+        <v>194.75</v>
+      </c>
+      <c r="G20" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="47">
         <v>18</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="63">
-        <v>172.74680630994109</v>
-      </c>
-      <c r="F21" s="63">
-        <v>172.74680630994109</v>
-      </c>
-      <c r="G21" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="49">
+      <c r="D21" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="60">
+        <v>172.75</v>
+      </c>
+      <c r="F21" s="60">
+        <v>172.75</v>
+      </c>
+      <c r="G21" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="46">
         <v>19</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="63">
-        <v>150.74680630994109</v>
-      </c>
-      <c r="F22" s="63">
-        <v>150.74680630994109</v>
-      </c>
-      <c r="G22" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H22" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50">
+      <c r="D22" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="60">
+        <v>150.75</v>
+      </c>
+      <c r="F22" s="60">
+        <v>150.75</v>
+      </c>
+      <c r="G22" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="47">
         <v>20</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="63">
-        <v>128.74680630994109</v>
-      </c>
-      <c r="F23" s="63">
-        <v>128.74680630994109</v>
-      </c>
-      <c r="G23" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H23" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50">
+      <c r="D23" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="60">
+        <v>128.75</v>
+      </c>
+      <c r="F23" s="60">
+        <v>128.75</v>
+      </c>
+      <c r="G23" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="47">
         <v>21</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="63">
-        <v>106.74680630994111</v>
-      </c>
-      <c r="F24" s="63">
-        <v>106.74680630994111</v>
-      </c>
-      <c r="G24" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50">
+      <c r="D24" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="60">
+        <v>106.75</v>
+      </c>
+      <c r="F24" s="60">
+        <v>106.75</v>
+      </c>
+      <c r="G24" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="47">
         <v>22</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="63">
-        <v>84.746806309941064</v>
-      </c>
-      <c r="F25" s="63">
-        <v>84.746806309941064</v>
-      </c>
-      <c r="G25" s="44">
-        <v>1000</v>
-      </c>
-      <c r="H25" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-    </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-    </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-    </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-    </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-    </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-    </row>
-    <row r="33" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D25" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="60">
+        <v>84.75</v>
+      </c>
+      <c r="F25" s="60">
+        <v>84.75</v>
+      </c>
+      <c r="G25" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H25" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="47">
+        <v>23</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="59">
+        <v>43.59</v>
+      </c>
+      <c r="F26" s="59">
+        <v>43.59</v>
+      </c>
+      <c r="G26" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H26" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="47">
+        <v>24</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="59">
+        <v>65.59</v>
+      </c>
+      <c r="F27" s="59">
+        <v>65.59</v>
+      </c>
+      <c r="G27" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="47">
+        <v>25</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="59">
+        <v>87.59</v>
+      </c>
+      <c r="F28" s="59">
+        <v>87.59</v>
+      </c>
+      <c r="G28" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="47">
+        <v>26</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="59">
+        <v>109.59</v>
+      </c>
+      <c r="F29" s="59">
+        <v>109.59</v>
+      </c>
+      <c r="G29" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="47">
+        <v>27</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="59">
+        <v>131.59</v>
+      </c>
+      <c r="F30" s="59">
+        <v>131.59</v>
+      </c>
+      <c r="G30" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="47">
+        <v>28</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="59">
+        <v>153.59</v>
+      </c>
+      <c r="F31" s="59">
+        <v>153.59</v>
+      </c>
+      <c r="G31" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47">
+        <v>29</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="59">
+        <v>175.59</v>
+      </c>
+      <c r="F32" s="59">
+        <v>175.59</v>
+      </c>
+      <c r="G32" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="47">
+        <v>30</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="59">
+        <v>197.59</v>
+      </c>
+      <c r="F33" s="59">
+        <v>197.59</v>
+      </c>
+      <c r="G33" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="47">
+        <v>31</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="59">
+        <v>176.9</v>
+      </c>
+      <c r="F34" s="59">
+        <v>176.9</v>
+      </c>
+      <c r="G34" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H34" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="47">
+        <v>32</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="59">
+        <v>154.9</v>
+      </c>
+      <c r="F35" s="59">
+        <v>154.9</v>
+      </c>
+      <c r="G35" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H35" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="47">
+        <v>33</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="59">
+        <v>132.9</v>
+      </c>
+      <c r="F36" s="59">
+        <v>132.9</v>
+      </c>
+      <c r="G36" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H36" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="47">
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="59">
+        <v>110.9</v>
+      </c>
+      <c r="F37" s="59">
+        <v>110.9</v>
+      </c>
+      <c r="G37" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H37" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="47">
+        <v>35</v>
+      </c>
+      <c r="B38" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="59">
+        <v>72.03</v>
+      </c>
+      <c r="F38" s="59">
+        <v>72.03</v>
+      </c>
+      <c r="G38" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H38" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="47">
+        <v>36</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="59">
+        <v>94.03</v>
+      </c>
+      <c r="F39" s="59">
+        <v>94.03</v>
+      </c>
+      <c r="G39" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H39" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="47">
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="59">
+        <v>116.03</v>
+      </c>
+      <c r="F40" s="59">
+        <v>116.03</v>
+      </c>
+      <c r="G40" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H40" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="47">
+        <v>38</v>
+      </c>
+      <c r="B41" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="59">
+        <v>138.03</v>
+      </c>
+      <c r="F41" s="59">
+        <v>138.03</v>
+      </c>
+      <c r="G41" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H41" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="47">
+        <v>39</v>
+      </c>
+      <c r="B42" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="59">
+        <v>160.03</v>
+      </c>
+      <c r="F42" s="59">
+        <v>160.03</v>
+      </c>
+      <c r="G42" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H42" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="47">
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="59">
+        <v>182.03</v>
+      </c>
+      <c r="F43" s="59">
+        <v>182.03</v>
+      </c>
+      <c r="G43" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="47">
+        <v>41</v>
+      </c>
+      <c r="B44" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="59">
+        <v>190.75</v>
+      </c>
+      <c r="F44" s="59">
+        <v>190.75</v>
+      </c>
+      <c r="G44" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="47">
+        <v>42</v>
+      </c>
+      <c r="B45" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="59">
+        <v>168.75</v>
+      </c>
+      <c r="F45" s="59">
+        <v>168.75</v>
+      </c>
+      <c r="G45" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H45" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="47">
+        <v>43</v>
+      </c>
+      <c r="B46" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="59">
+        <v>146.75</v>
+      </c>
+      <c r="F46" s="59">
+        <v>146.75</v>
+      </c>
+      <c r="G46" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H46" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="47">
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="59">
+        <v>124.75</v>
+      </c>
+      <c r="F47" s="59">
+        <v>124.75</v>
+      </c>
+      <c r="G47" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="47">
+        <v>45</v>
+      </c>
+      <c r="B48" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="59">
+        <v>102.75</v>
+      </c>
+      <c r="F48" s="59">
+        <v>102.75</v>
+      </c>
+      <c r="G48" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="47">
+        <v>46</v>
+      </c>
+      <c r="B49" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="59">
+        <v>80.75</v>
+      </c>
+      <c r="F49" s="59">
+        <v>80.75</v>
+      </c>
+      <c r="G49" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H49" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="47">
+        <v>47</v>
+      </c>
+      <c r="B50" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" s="59">
+        <v>46.59</v>
+      </c>
+      <c r="F50" s="59">
+        <v>46.59</v>
+      </c>
+      <c r="G50" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H50" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="47">
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" s="59">
+        <v>68.59</v>
+      </c>
+      <c r="F51" s="59">
+        <v>68.59</v>
+      </c>
+      <c r="G51" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H51" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="47">
+        <v>49</v>
+      </c>
+      <c r="B52" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="59">
+        <v>90.59</v>
+      </c>
+      <c r="F52" s="59">
+        <v>90.59</v>
+      </c>
+      <c r="G52" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="47">
+        <v>50</v>
+      </c>
+      <c r="B53" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="59">
+        <v>112.59</v>
+      </c>
+      <c r="F53" s="59">
+        <v>112.59</v>
+      </c>
+      <c r="G53" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H53" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="47">
+        <v>51</v>
+      </c>
+      <c r="B54" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="59">
+        <v>134.59</v>
+      </c>
+      <c r="F54" s="59">
+        <v>134.59</v>
+      </c>
+      <c r="G54" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H54" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="47">
+        <v>52</v>
+      </c>
+      <c r="B55" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55" s="59">
+        <v>156.59</v>
+      </c>
+      <c r="F55" s="59">
+        <v>156.59</v>
+      </c>
+      <c r="G55" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H55" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="47">
+        <v>53</v>
+      </c>
+      <c r="B56" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="59">
+        <v>178.59</v>
+      </c>
+      <c r="F56" s="59">
+        <v>178.59</v>
+      </c>
+      <c r="G56" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H56" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="47">
+        <v>54</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="59">
+        <v>195.9</v>
+      </c>
+      <c r="F57" s="59">
+        <v>195.9</v>
+      </c>
+      <c r="G57" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="47">
+        <v>55</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="59">
+        <v>173.9</v>
+      </c>
+      <c r="F58" s="59">
+        <v>173.9</v>
+      </c>
+      <c r="G58" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="47">
+        <v>56</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="59">
+        <v>151.9</v>
+      </c>
+      <c r="F59" s="59">
+        <v>151.9</v>
+      </c>
+      <c r="G59" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="47">
+        <v>57</v>
+      </c>
+      <c r="B60" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="59">
+        <v>129.9</v>
+      </c>
+      <c r="F60" s="59">
+        <v>129.9</v>
+      </c>
+      <c r="G60" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H60" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="47">
+        <v>58</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61" s="59">
+        <v>107.9</v>
+      </c>
+      <c r="F61" s="59">
+        <v>107.9</v>
+      </c>
+      <c r="G61" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="47">
+        <v>59</v>
+      </c>
+      <c r="B62" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D62" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="59">
+        <v>75.03</v>
+      </c>
+      <c r="F62" s="59">
+        <v>75.03</v>
+      </c>
+      <c r="G62" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="47">
+        <v>60</v>
+      </c>
+      <c r="B63" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="59">
+        <v>97.03</v>
+      </c>
+      <c r="F63" s="59">
+        <v>97.03</v>
+      </c>
+      <c r="G63" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H63" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="47">
+        <v>61</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D64" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" s="59">
+        <v>119.03</v>
+      </c>
+      <c r="F64" s="59">
+        <v>119.03</v>
+      </c>
+      <c r="G64" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H64" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="47">
+        <v>62</v>
+      </c>
+      <c r="B65" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C65" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D65" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" s="59">
+        <v>141.03</v>
+      </c>
+      <c r="F65" s="59">
+        <v>141.03</v>
+      </c>
+      <c r="G65" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H65" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="47">
+        <v>63</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="59">
+        <v>163.03</v>
+      </c>
+      <c r="F66" s="59">
+        <v>163.03</v>
+      </c>
+      <c r="G66" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H66" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="47">
+        <v>64</v>
+      </c>
+      <c r="B67" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E67" s="59">
+        <v>185.03</v>
+      </c>
+      <c r="F67" s="59">
+        <v>185.03</v>
+      </c>
+      <c r="G67" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H67" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="47">
+        <v>65</v>
+      </c>
+      <c r="B68" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="C68" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" s="59">
+        <v>187.75</v>
+      </c>
+      <c r="F68" s="59">
+        <v>187.75</v>
+      </c>
+      <c r="G68" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H68" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="47">
+        <v>66</v>
+      </c>
+      <c r="B69" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D69" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="59">
+        <v>165.75</v>
+      </c>
+      <c r="F69" s="59">
+        <v>165.75</v>
+      </c>
+      <c r="G69" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H69" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="47">
+        <v>67</v>
+      </c>
+      <c r="B70" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="59">
+        <v>143.75</v>
+      </c>
+      <c r="F70" s="59">
+        <v>143.75</v>
+      </c>
+      <c r="G70" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H70" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="47">
+        <v>68</v>
+      </c>
+      <c r="B71" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" s="59">
+        <v>121.75</v>
+      </c>
+      <c r="F71" s="59">
+        <v>121.75</v>
+      </c>
+      <c r="G71" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H71" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="47">
+        <v>69</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="59">
+        <v>99.75</v>
+      </c>
+      <c r="F72" s="59">
+        <v>99.75</v>
+      </c>
+      <c r="G72" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H72" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="47">
+        <v>70</v>
+      </c>
+      <c r="B73" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73" s="59">
+        <v>77.75</v>
+      </c>
+      <c r="F73" s="59">
+        <v>77.75</v>
+      </c>
+      <c r="G73" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H73" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="47">
+        <v>71</v>
+      </c>
+      <c r="B74" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D74" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" s="59">
+        <v>50.59</v>
+      </c>
+      <c r="F74" s="59">
+        <v>50.59</v>
+      </c>
+      <c r="G74" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H74" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="47">
+        <v>72</v>
+      </c>
+      <c r="B75" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75" s="59">
+        <v>72.59</v>
+      </c>
+      <c r="F75" s="59">
+        <v>72.59</v>
+      </c>
+      <c r="G75" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H75" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="47">
+        <v>73</v>
+      </c>
+      <c r="B76" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D76" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="59">
+        <v>94.59</v>
+      </c>
+      <c r="F76" s="59">
+        <v>94.59</v>
+      </c>
+      <c r="G76" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H76" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="47">
+        <v>74</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77" s="59">
+        <v>116.59</v>
+      </c>
+      <c r="F77" s="59">
+        <v>116.59</v>
+      </c>
+      <c r="G77" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H77" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="47">
+        <v>75</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E78" s="59">
+        <v>138.59</v>
+      </c>
+      <c r="F78" s="59">
+        <v>138.59</v>
+      </c>
+      <c r="G78" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H78" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="47">
+        <v>76</v>
+      </c>
+      <c r="B79" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D79" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E79" s="59">
+        <v>160.59</v>
+      </c>
+      <c r="F79" s="59">
+        <v>160.59</v>
+      </c>
+      <c r="G79" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H79" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="47">
+        <v>77</v>
+      </c>
+      <c r="B80" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D80" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80" s="59">
+        <v>182.59</v>
+      </c>
+      <c r="F80" s="59">
+        <v>182.59</v>
+      </c>
+      <c r="G80" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H80" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="47">
+        <v>78</v>
+      </c>
+      <c r="B81" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D81" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="59">
+        <v>191.9</v>
+      </c>
+      <c r="F81" s="59">
+        <v>191.9</v>
+      </c>
+      <c r="G81" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="47">
+        <v>79</v>
+      </c>
+      <c r="B82" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C82" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D82" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="59">
+        <v>169.9</v>
+      </c>
+      <c r="F82" s="59">
+        <v>169.9</v>
+      </c>
+      <c r="G82" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H82" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="47">
+        <v>80</v>
+      </c>
+      <c r="B83" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D83" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="59">
+        <v>147.9</v>
+      </c>
+      <c r="F83" s="59">
+        <v>147.9</v>
+      </c>
+      <c r="G83" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="47">
+        <v>81</v>
+      </c>
+      <c r="B84" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D84" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E84" s="59">
+        <v>125.9</v>
+      </c>
+      <c r="F84" s="59">
+        <v>125.9</v>
+      </c>
+      <c r="G84" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H84" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="47">
+        <v>82</v>
+      </c>
+      <c r="B85" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D85" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="59">
+        <v>103.9</v>
+      </c>
+      <c r="F85" s="59">
+        <v>103.9</v>
+      </c>
+      <c r="G85" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H85" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="47">
+        <v>83</v>
+      </c>
+      <c r="B86" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="59">
+        <v>79.03</v>
+      </c>
+      <c r="F86" s="59">
+        <v>79.03</v>
+      </c>
+      <c r="G86" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H86" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="47">
+        <v>84</v>
+      </c>
+      <c r="B87" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="59">
+        <v>101.03</v>
+      </c>
+      <c r="F87" s="59">
+        <v>101.03</v>
+      </c>
+      <c r="G87" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H87" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="47">
+        <v>85</v>
+      </c>
+      <c r="B88" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E88" s="59">
+        <v>123.03</v>
+      </c>
+      <c r="F88" s="59">
+        <v>123.03</v>
+      </c>
+      <c r="G88" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H88" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="47">
+        <v>86</v>
+      </c>
+      <c r="B89" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="59">
+        <v>145.03</v>
+      </c>
+      <c r="F89" s="59">
+        <v>145.03</v>
+      </c>
+      <c r="G89" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H89" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="47">
+        <v>87</v>
+      </c>
+      <c r="B90" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" s="59">
+        <v>167.03</v>
+      </c>
+      <c r="F90" s="59">
+        <v>167.03</v>
+      </c>
+      <c r="G90" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H90" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="47">
+        <v>88</v>
+      </c>
+      <c r="B91" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="59">
+        <v>189.03</v>
+      </c>
+      <c r="F91" s="59">
+        <v>189.03</v>
+      </c>
+      <c r="G91" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H91" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="47">
+        <v>89</v>
+      </c>
+      <c r="B92" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92" s="59">
+        <v>183.75</v>
+      </c>
+      <c r="F92" s="59">
+        <v>183.75</v>
+      </c>
+      <c r="G92" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H92" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="47">
+        <v>90</v>
+      </c>
+      <c r="B93" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D93" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E93" s="59">
+        <v>161.75</v>
+      </c>
+      <c r="F93" s="59">
+        <v>161.75</v>
+      </c>
+      <c r="G93" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="47">
+        <v>91</v>
+      </c>
+      <c r="B94" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="59">
+        <v>139.75</v>
+      </c>
+      <c r="F94" s="59">
+        <v>139.75</v>
+      </c>
+      <c r="G94" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H94" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="47">
+        <v>92</v>
+      </c>
+      <c r="B95" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="59">
+        <v>117.75</v>
+      </c>
+      <c r="F95" s="59">
+        <v>117.75</v>
+      </c>
+      <c r="G95" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="47">
+        <v>93</v>
+      </c>
+      <c r="B96" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="C96" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D96" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="59">
+        <v>95.75</v>
+      </c>
+      <c r="F96" s="59">
+        <v>95.75</v>
+      </c>
+      <c r="G96" s="41">
+        <v>1000</v>
+      </c>
+      <c r="H96" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -2594,7 +4823,7 @@
       <c r="F97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -2603,436 +4832,436 @@
       <c r="F98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="51"/>
-      <c r="B99" s="59"/>
-      <c r="C99" s="57"/>
-      <c r="D99" s="36"/>
-      <c r="G99" s="37"/>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="48"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="54"/>
+      <c r="D99" s="33"/>
+      <c r="G99" s="34"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="52"/>
-      <c r="B100" s="59"/>
-      <c r="C100" s="57"/>
-      <c r="D100" s="36"/>
-      <c r="G100" s="37"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="49"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="33"/>
+      <c r="G100" s="34"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="53"/>
-      <c r="B101" s="59"/>
-      <c r="C101" s="57"/>
-      <c r="D101" s="36"/>
-      <c r="G101" s="37"/>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="50"/>
+      <c r="B101" s="56"/>
+      <c r="C101" s="54"/>
+      <c r="D101" s="33"/>
+      <c r="G101" s="34"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="53"/>
-      <c r="B102" s="59"/>
-      <c r="C102" s="57"/>
-      <c r="D102" s="36"/>
-      <c r="G102" s="37"/>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="50"/>
+      <c r="B102" s="56"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="33"/>
+      <c r="G102" s="34"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="53"/>
-      <c r="B103" s="59"/>
-      <c r="C103" s="57"/>
-      <c r="D103" s="36"/>
-      <c r="G103" s="37"/>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="50"/>
+      <c r="B103" s="56"/>
+      <c r="C103" s="54"/>
+      <c r="D103" s="33"/>
+      <c r="G103" s="34"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="51"/>
-      <c r="B104" s="59"/>
-      <c r="C104" s="57"/>
-      <c r="D104" s="36"/>
-      <c r="G104" s="37"/>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="48"/>
+      <c r="B104" s="56"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="33"/>
+      <c r="G104" s="34"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="52"/>
-      <c r="B105" s="59"/>
-      <c r="C105" s="57"/>
-      <c r="D105" s="36"/>
-      <c r="G105" s="37"/>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="49"/>
+      <c r="B105" s="56"/>
+      <c r="C105" s="54"/>
+      <c r="D105" s="33"/>
+      <c r="G105" s="34"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="53"/>
-      <c r="B106" s="59"/>
-      <c r="C106" s="57"/>
-      <c r="D106" s="36"/>
-      <c r="G106" s="37"/>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="50"/>
+      <c r="B106" s="56"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="33"/>
+      <c r="G106" s="34"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="53"/>
-      <c r="B107" s="59"/>
-      <c r="C107" s="57"/>
-      <c r="D107" s="36"/>
-      <c r="G107" s="37"/>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="50"/>
+      <c r="B107" s="56"/>
+      <c r="C107" s="54"/>
+      <c r="D107" s="33"/>
+      <c r="G107" s="34"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="53"/>
-      <c r="B108" s="59"/>
-      <c r="C108" s="57"/>
-      <c r="D108" s="36"/>
-      <c r="G108" s="37"/>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="50"/>
+      <c r="B108" s="56"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="33"/>
+      <c r="G108" s="34"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="51"/>
-      <c r="B109" s="59"/>
-      <c r="C109" s="57"/>
-      <c r="D109" s="36"/>
-      <c r="G109" s="37"/>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="48"/>
+      <c r="B109" s="56"/>
+      <c r="C109" s="54"/>
+      <c r="D109" s="33"/>
+      <c r="G109" s="34"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="52"/>
-      <c r="B110" s="59"/>
-      <c r="C110" s="57"/>
-      <c r="D110" s="36"/>
-      <c r="G110" s="37"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="49"/>
+      <c r="B110" s="56"/>
+      <c r="C110" s="54"/>
+      <c r="D110" s="33"/>
+      <c r="G110" s="34"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="53"/>
-      <c r="B111" s="59"/>
-      <c r="C111" s="57"/>
-      <c r="D111" s="36"/>
-      <c r="G111" s="37"/>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="50"/>
+      <c r="B111" s="56"/>
+      <c r="C111" s="54"/>
+      <c r="D111" s="33"/>
+      <c r="G111" s="34"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="53"/>
-      <c r="B112" s="59"/>
-      <c r="C112" s="57"/>
-      <c r="D112" s="36"/>
-      <c r="G112" s="37"/>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="50"/>
+      <c r="B112" s="56"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="33"/>
+      <c r="G112" s="34"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="53"/>
-      <c r="B113" s="59"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="36"/>
-      <c r="G113" s="37"/>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="50"/>
+      <c r="B113" s="56"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="33"/>
+      <c r="G113" s="34"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="51"/>
-      <c r="B114" s="59"/>
-      <c r="C114" s="57"/>
-      <c r="D114" s="36"/>
-      <c r="G114" s="37"/>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="48"/>
+      <c r="B114" s="56"/>
+      <c r="C114" s="54"/>
+      <c r="D114" s="33"/>
+      <c r="G114" s="34"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="52"/>
-      <c r="B115" s="59"/>
-      <c r="C115" s="57"/>
-      <c r="D115" s="36"/>
-      <c r="G115" s="37"/>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="49"/>
+      <c r="B115" s="56"/>
+      <c r="C115" s="54"/>
+      <c r="D115" s="33"/>
+      <c r="G115" s="34"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="53"/>
-      <c r="B116" s="59"/>
-      <c r="C116" s="57"/>
-      <c r="D116" s="36"/>
-      <c r="G116" s="37"/>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="50"/>
+      <c r="B116" s="56"/>
+      <c r="C116" s="54"/>
+      <c r="D116" s="33"/>
+      <c r="G116" s="34"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="53"/>
-      <c r="B117" s="59"/>
-      <c r="C117" s="57"/>
-      <c r="D117" s="36"/>
-      <c r="G117" s="37"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="50"/>
+      <c r="B117" s="56"/>
+      <c r="C117" s="54"/>
+      <c r="D117" s="33"/>
+      <c r="G117" s="34"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="53"/>
-      <c r="B118" s="59"/>
-      <c r="C118" s="57"/>
-      <c r="D118" s="36"/>
-      <c r="G118" s="37"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="50"/>
+      <c r="B118" s="56"/>
+      <c r="C118" s="54"/>
+      <c r="D118" s="33"/>
+      <c r="G118" s="34"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="51"/>
-      <c r="B119" s="59"/>
-      <c r="C119" s="57"/>
-      <c r="D119" s="36"/>
-      <c r="G119" s="37"/>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="48"/>
+      <c r="B119" s="56"/>
+      <c r="C119" s="54"/>
+      <c r="D119" s="33"/>
+      <c r="G119" s="34"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="52"/>
-      <c r="B120" s="59"/>
-      <c r="C120" s="57"/>
-      <c r="D120" s="36"/>
-      <c r="G120" s="37"/>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="49"/>
+      <c r="B120" s="56"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="33"/>
+      <c r="G120" s="34"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="53"/>
-      <c r="B121" s="59"/>
-      <c r="C121" s="57"/>
-      <c r="D121" s="36"/>
-      <c r="G121" s="37"/>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="50"/>
+      <c r="B121" s="56"/>
+      <c r="C121" s="54"/>
+      <c r="D121" s="33"/>
+      <c r="G121" s="34"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="53"/>
-      <c r="B122" s="59"/>
-      <c r="C122" s="57"/>
-      <c r="D122" s="36"/>
-      <c r="G122" s="37"/>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="50"/>
+      <c r="B122" s="56"/>
+      <c r="C122" s="54"/>
+      <c r="D122" s="33"/>
+      <c r="G122" s="34"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="53"/>
-      <c r="B123" s="59"/>
-      <c r="C123" s="57"/>
-      <c r="D123" s="36"/>
-      <c r="G123" s="37"/>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="50"/>
+      <c r="B123" s="56"/>
+      <c r="C123" s="54"/>
+      <c r="D123" s="33"/>
+      <c r="G123" s="34"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="51"/>
-      <c r="B124" s="59"/>
-      <c r="C124" s="57"/>
-      <c r="D124" s="36"/>
-      <c r="G124" s="37"/>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="48"/>
+      <c r="B124" s="56"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="33"/>
+      <c r="G124" s="34"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="52"/>
-      <c r="B125" s="59"/>
-      <c r="C125" s="57"/>
-      <c r="D125" s="36"/>
-      <c r="G125" s="37"/>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="49"/>
+      <c r="B125" s="56"/>
+      <c r="C125" s="54"/>
+      <c r="D125" s="33"/>
+      <c r="G125" s="34"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="53"/>
-      <c r="B126" s="59"/>
-      <c r="C126" s="57"/>
-      <c r="D126" s="36"/>
-      <c r="G126" s="37"/>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="50"/>
+      <c r="B126" s="56"/>
+      <c r="C126" s="54"/>
+      <c r="D126" s="33"/>
+      <c r="G126" s="34"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="53"/>
-      <c r="B127" s="59"/>
-      <c r="C127" s="57"/>
-      <c r="D127" s="36"/>
-      <c r="G127" s="37"/>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="50"/>
+      <c r="B127" s="56"/>
+      <c r="C127" s="54"/>
+      <c r="D127" s="33"/>
+      <c r="G127" s="34"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="53"/>
-      <c r="B128" s="59"/>
-      <c r="C128" s="57"/>
-      <c r="D128" s="36"/>
-      <c r="G128" s="37"/>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="50"/>
+      <c r="B128" s="56"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="33"/>
+      <c r="G128" s="34"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="51"/>
-      <c r="B129" s="59"/>
-      <c r="C129" s="57"/>
-      <c r="D129" s="36"/>
-      <c r="G129" s="37"/>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="48"/>
+      <c r="B129" s="56"/>
+      <c r="C129" s="54"/>
+      <c r="D129" s="33"/>
+      <c r="G129" s="34"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="52"/>
-      <c r="B130" s="59"/>
-      <c r="C130" s="57"/>
-      <c r="D130" s="36"/>
-      <c r="G130" s="37"/>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="49"/>
+      <c r="B130" s="56"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="33"/>
+      <c r="G130" s="34"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="53"/>
-      <c r="B131" s="59"/>
-      <c r="C131" s="57"/>
-      <c r="D131" s="36"/>
-      <c r="G131" s="37"/>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="50"/>
+      <c r="B131" s="56"/>
+      <c r="C131" s="54"/>
+      <c r="D131" s="33"/>
+      <c r="G131" s="34"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="53"/>
-      <c r="B132" s="59"/>
-      <c r="C132" s="57"/>
-      <c r="D132" s="36"/>
-      <c r="G132" s="37"/>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="50"/>
+      <c r="B132" s="56"/>
+      <c r="C132" s="54"/>
+      <c r="D132" s="33"/>
+      <c r="G132" s="34"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="53"/>
-      <c r="B133" s="59"/>
-      <c r="C133" s="57"/>
-      <c r="D133" s="36"/>
-      <c r="G133" s="37"/>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="50"/>
+      <c r="B133" s="56"/>
+      <c r="C133" s="54"/>
+      <c r="D133" s="33"/>
+      <c r="G133" s="34"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="51"/>
-      <c r="B134" s="59"/>
-      <c r="C134" s="57"/>
-      <c r="D134" s="36"/>
-      <c r="G134" s="37"/>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="48"/>
+      <c r="B134" s="56"/>
+      <c r="C134" s="54"/>
+      <c r="D134" s="33"/>
+      <c r="G134" s="34"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="52"/>
-      <c r="B135" s="59"/>
-      <c r="C135" s="57"/>
-      <c r="D135" s="36"/>
-      <c r="G135" s="37"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="49"/>
+      <c r="B135" s="56"/>
+      <c r="C135" s="54"/>
+      <c r="D135" s="33"/>
+      <c r="G135" s="34"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="53"/>
-      <c r="B136" s="59"/>
-      <c r="C136" s="57"/>
-      <c r="D136" s="36"/>
-      <c r="G136" s="37"/>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="50"/>
+      <c r="B136" s="56"/>
+      <c r="C136" s="54"/>
+      <c r="D136" s="33"/>
+      <c r="G136" s="34"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="53"/>
-      <c r="B137" s="59"/>
-      <c r="C137" s="57"/>
-      <c r="D137" s="36"/>
-      <c r="G137" s="37"/>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="50"/>
+      <c r="B137" s="56"/>
+      <c r="C137" s="54"/>
+      <c r="D137" s="33"/>
+      <c r="G137" s="34"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="53"/>
-      <c r="B138" s="59"/>
-      <c r="C138" s="57"/>
-      <c r="D138" s="36"/>
-      <c r="G138" s="37"/>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="50"/>
+      <c r="B138" s="56"/>
+      <c r="C138" s="54"/>
+      <c r="D138" s="33"/>
+      <c r="G138" s="34"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="51"/>
-      <c r="B139" s="59"/>
-      <c r="C139" s="57"/>
-      <c r="D139" s="36"/>
-      <c r="G139" s="37"/>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="48"/>
+      <c r="B139" s="56"/>
+      <c r="C139" s="54"/>
+      <c r="D139" s="33"/>
+      <c r="G139" s="34"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="52"/>
-      <c r="B140" s="59"/>
-      <c r="C140" s="57"/>
-      <c r="D140" s="36"/>
-      <c r="G140" s="37"/>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="49"/>
+      <c r="B140" s="56"/>
+      <c r="C140" s="54"/>
+      <c r="D140" s="33"/>
+      <c r="G140" s="34"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="53"/>
-      <c r="B141" s="59"/>
-      <c r="C141" s="57"/>
-      <c r="D141" s="36"/>
-      <c r="G141" s="37"/>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="50"/>
+      <c r="B141" s="56"/>
+      <c r="C141" s="54"/>
+      <c r="D141" s="33"/>
+      <c r="G141" s="34"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="53"/>
-      <c r="B142" s="59"/>
-      <c r="C142" s="57"/>
-      <c r="D142" s="36"/>
-      <c r="G142" s="37"/>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="50"/>
+      <c r="B142" s="56"/>
+      <c r="C142" s="54"/>
+      <c r="D142" s="33"/>
+      <c r="G142" s="34"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="53"/>
-      <c r="B143" s="59"/>
-      <c r="C143" s="57"/>
-      <c r="D143" s="36"/>
-      <c r="G143" s="37"/>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="50"/>
+      <c r="B143" s="56"/>
+      <c r="C143" s="54"/>
+      <c r="D143" s="33"/>
+      <c r="G143" s="34"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="51"/>
-      <c r="B144" s="59"/>
-      <c r="C144" s="57"/>
-      <c r="D144" s="36"/>
-      <c r="G144" s="37"/>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="48"/>
+      <c r="B144" s="56"/>
+      <c r="C144" s="54"/>
+      <c r="D144" s="33"/>
+      <c r="G144" s="34"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="52"/>
-      <c r="B145" s="59"/>
-      <c r="C145" s="57"/>
-      <c r="D145" s="36"/>
-      <c r="G145" s="37"/>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="49"/>
+      <c r="B145" s="56"/>
+      <c r="C145" s="54"/>
+      <c r="D145" s="33"/>
+      <c r="G145" s="34"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="53"/>
-      <c r="B146" s="59"/>
-      <c r="C146" s="57"/>
-      <c r="D146" s="36"/>
-      <c r="G146" s="37"/>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="50"/>
+      <c r="B146" s="56"/>
+      <c r="C146" s="54"/>
+      <c r="D146" s="33"/>
+      <c r="G146" s="34"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="53"/>
-      <c r="B147" s="59"/>
-      <c r="C147" s="57"/>
-      <c r="D147" s="36"/>
-      <c r="G147" s="37"/>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="50"/>
+      <c r="B147" s="56"/>
+      <c r="C147" s="54"/>
+      <c r="D147" s="33"/>
+      <c r="G147" s="34"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="53"/>
-      <c r="B148" s="59"/>
-      <c r="C148" s="57"/>
-      <c r="D148" s="36"/>
-      <c r="G148" s="37"/>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="50"/>
+      <c r="B148" s="56"/>
+      <c r="C148" s="54"/>
+      <c r="D148" s="33"/>
+      <c r="G148" s="34"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="51"/>
-      <c r="B149" s="59"/>
-      <c r="C149" s="57"/>
-      <c r="D149" s="36"/>
-      <c r="G149" s="37"/>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="48"/>
+      <c r="B149" s="56"/>
+      <c r="C149" s="54"/>
+      <c r="D149" s="33"/>
+      <c r="G149" s="34"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="52"/>
-      <c r="B150" s="59"/>
-      <c r="C150" s="57"/>
-      <c r="D150" s="36"/>
-      <c r="G150" s="37"/>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="49"/>
+      <c r="B150" s="56"/>
+      <c r="C150" s="54"/>
+      <c r="D150" s="33"/>
+      <c r="G150" s="34"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="53"/>
-      <c r="B151" s="59"/>
-      <c r="C151" s="57"/>
-      <c r="D151" s="36"/>
-      <c r="G151" s="37"/>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="50"/>
+      <c r="B151" s="56"/>
+      <c r="C151" s="54"/>
+      <c r="D151" s="33"/>
+      <c r="G151" s="34"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="53"/>
-      <c r="B152" s="59"/>
-      <c r="C152" s="57"/>
-      <c r="D152" s="36"/>
-      <c r="G152" s="37"/>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="50"/>
+      <c r="B152" s="56"/>
+      <c r="C152" s="54"/>
+      <c r="D152" s="33"/>
+      <c r="G152" s="34"/>
       <c r="H152" s="8"/>
     </row>
   </sheetData>
@@ -3047,14 +5276,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3065,7 +5294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3076,7 +5305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -3095,9 +5324,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3120,7 +5349,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3143,7 +5372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3166,7 +5395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3197,9 +5426,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3221,14 +5450,14 @@
       <c r="G1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="63" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3250,14 +5479,14 @@
       <c r="G2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="63" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3279,10 +5508,10 @@
       <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="H3" s="67">
-        <v>1000</v>
-      </c>
-      <c r="I3" s="68">
+      <c r="H3" s="64">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="65">
         <v>1</v>
       </c>
     </row>
@@ -3294,9 +5523,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D0F496-F61D-4678-8E5E-760759FAC311}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3313,7 +5542,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -3330,7 +5559,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>

--- a/data/Escenarios_Gx/320kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC280CF-3E6F-485E-A98B-73E8EA598A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFDD2D6-94D0-432D-B8F3-8A8E84F2B906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -4823,7 +4823,7 @@
       <c r="F97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -4832,269 +4832,302 @@
       <c r="F98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="48"/>
-      <c r="B99" s="56"/>
-      <c r="C99" s="54"/>
-      <c r="D99" s="33"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="8"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="49"/>
-      <c r="B100" s="56"/>
-      <c r="C100" s="54"/>
-      <c r="D100" s="33"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="8"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
-      <c r="B101" s="56"/>
-      <c r="C101" s="54"/>
-      <c r="D101" s="33"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="8"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="50"/>
-      <c r="B102" s="56"/>
-      <c r="C102" s="54"/>
-      <c r="D102" s="33"/>
-      <c r="G102" s="34"/>
-      <c r="H102" s="8"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="50"/>
-      <c r="B103" s="56"/>
-      <c r="C103" s="54"/>
-      <c r="D103" s="33"/>
-      <c r="G103" s="34"/>
-      <c r="H103" s="8"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="48"/>
-      <c r="B104" s="56"/>
-      <c r="C104" s="54"/>
-      <c r="D104" s="33"/>
-      <c r="G104" s="34"/>
-      <c r="H104" s="8"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="49"/>
-      <c r="B105" s="56"/>
-      <c r="C105" s="54"/>
-      <c r="D105" s="33"/>
-      <c r="G105" s="34"/>
-      <c r="H105" s="8"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="50"/>
-      <c r="B106" s="56"/>
-      <c r="C106" s="54"/>
-      <c r="D106" s="33"/>
-      <c r="G106" s="34"/>
-      <c r="H106" s="8"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="50"/>
-      <c r="B107" s="56"/>
-      <c r="C107" s="54"/>
-      <c r="D107" s="33"/>
-      <c r="G107" s="34"/>
-      <c r="H107" s="8"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="50"/>
-      <c r="B108" s="56"/>
-      <c r="C108" s="54"/>
-      <c r="D108" s="33"/>
-      <c r="G108" s="34"/>
-      <c r="H108" s="8"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="48"/>
-      <c r="B109" s="56"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="33"/>
-      <c r="G109" s="34"/>
-      <c r="H109" s="8"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="49"/>
-      <c r="B110" s="56"/>
-      <c r="C110" s="54"/>
-      <c r="D110" s="33"/>
-      <c r="G110" s="34"/>
-      <c r="H110" s="8"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="50"/>
-      <c r="B111" s="56"/>
-      <c r="C111" s="54"/>
-      <c r="D111" s="33"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="8"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="50"/>
-      <c r="B112" s="56"/>
-      <c r="C112" s="54"/>
-      <c r="D112" s="33"/>
-      <c r="G112" s="34"/>
-      <c r="H112" s="8"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="50"/>
-      <c r="B113" s="56"/>
-      <c r="C113" s="54"/>
-      <c r="D113" s="33"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="8"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="48"/>
-      <c r="B114" s="56"/>
-      <c r="C114" s="54"/>
-      <c r="D114" s="33"/>
-      <c r="G114" s="34"/>
-      <c r="H114" s="8"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="49"/>
-      <c r="B115" s="56"/>
-      <c r="C115" s="54"/>
-      <c r="D115" s="33"/>
-      <c r="G115" s="34"/>
-      <c r="H115" s="8"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="50"/>
-      <c r="B116" s="56"/>
-      <c r="C116" s="54"/>
-      <c r="D116" s="33"/>
-      <c r="G116" s="34"/>
-      <c r="H116" s="8"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="50"/>
-      <c r="B117" s="56"/>
-      <c r="C117" s="54"/>
-      <c r="D117" s="33"/>
-      <c r="G117" s="34"/>
-      <c r="H117" s="8"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="50"/>
-      <c r="B118" s="56"/>
-      <c r="C118" s="54"/>
-      <c r="D118" s="33"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="8"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="48"/>
-      <c r="B119" s="56"/>
-      <c r="C119" s="54"/>
-      <c r="D119" s="33"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="8"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="49"/>
-      <c r="B120" s="56"/>
-      <c r="C120" s="54"/>
-      <c r="D120" s="33"/>
-      <c r="G120" s="34"/>
-      <c r="H120" s="8"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="50"/>
-      <c r="B121" s="56"/>
-      <c r="C121" s="54"/>
-      <c r="D121" s="33"/>
-      <c r="G121" s="34"/>
-      <c r="H121" s="8"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="50"/>
-      <c r="B122" s="56"/>
-      <c r="C122" s="54"/>
-      <c r="D122" s="33"/>
-      <c r="G122" s="34"/>
-      <c r="H122" s="8"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="50"/>
-      <c r="B123" s="56"/>
-      <c r="C123" s="54"/>
-      <c r="D123" s="33"/>
-      <c r="G123" s="34"/>
-      <c r="H123" s="8"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="48"/>
-      <c r="B124" s="56"/>
-      <c r="C124" s="54"/>
-      <c r="D124" s="33"/>
-      <c r="G124" s="34"/>
-      <c r="H124" s="8"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="49"/>
-      <c r="B125" s="56"/>
-      <c r="C125" s="54"/>
-      <c r="D125" s="33"/>
-      <c r="G125" s="34"/>
-      <c r="H125" s="8"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="50"/>
-      <c r="B126" s="56"/>
-      <c r="C126" s="54"/>
-      <c r="D126" s="33"/>
-      <c r="G126" s="34"/>
-      <c r="H126" s="8"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="50"/>
-      <c r="B127" s="56"/>
-      <c r="C127" s="54"/>
-      <c r="D127" s="33"/>
-      <c r="G127" s="34"/>
-      <c r="H127" s="8"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="50"/>
-      <c r="B128" s="56"/>
-      <c r="C128" s="54"/>
-      <c r="D128" s="33"/>
-      <c r="G128" s="34"/>
-      <c r="H128" s="8"/>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="48"/>
-      <c r="B129" s="56"/>
-      <c r="C129" s="54"/>
-      <c r="D129" s="33"/>
-      <c r="G129" s="34"/>
-      <c r="H129" s="8"/>
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="49"/>
-      <c r="B130" s="56"/>
-      <c r="C130" s="54"/>
-      <c r="D130" s="33"/>
-      <c r="G130" s="34"/>
-      <c r="H130" s="8"/>
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="50"/>
-      <c r="B131" s="56"/>
-      <c r="C131" s="54"/>
-      <c r="D131" s="33"/>
-      <c r="G131" s="34"/>
-      <c r="H131" s="8"/>
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="50"/>
